--- a/data/cci/cci-dataType-ecv-mapping.xlsx
+++ b/data/cci/cci-dataType-ecv-mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{988F0833-324E-A94E-ADCC-47810A45B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AFE69F5-242E-4A0F-8B80-71710CC0167B}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{988F0833-324E-A94E-ADCC-47810A45B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9733AD3D-2347-4A42-A480-A10037525630}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4E51E550-2BE2-1645-BA80-54EF4527885D}"/>
+    <workbookView xWindow="9000" yWindow="2700" windowWidth="28800" windowHeight="15285" xr2:uid="{4E51E550-2BE2-1645-BA80-54EF4527885D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="118">
   <si>
     <t>dtype URI</t>
   </si>
@@ -373,6 +373,9 @@
   </si>
   <si>
     <t>cciecv_prec</t>
+  </si>
+  <si>
+    <t>dtype_nh3</t>
   </si>
 </sst>
 </file>
@@ -991,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03066BF4-F4E8-0F4A-A490-1A16D2F31AC9}">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2259,6 +2262,20 @@
         <v>116</v>
       </c>
       <c r="D90" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>117</v>
+      </c>
+      <c r="B91" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" t="s">
+        <v>116</v>
+      </c>
+      <c r="D91" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/cci/cci-dataType-ecv-mapping.xlsx
+++ b/data/cci/cci-dataType-ecv-mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{988F0833-324E-A94E-ADCC-47810A45B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9733AD3D-2347-4A42-A480-A10037525630}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{988F0833-324E-A94E-ADCC-47810A45B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43199E8C-6F20-480D-A352-BAE349986048}"/>
   <bookViews>
-    <workbookView xWindow="9000" yWindow="2700" windowWidth="28800" windowHeight="15285" xr2:uid="{4E51E550-2BE2-1645-BA80-54EF4527885D}"/>
+    <workbookView xWindow="39450" yWindow="3285" windowWidth="34515" windowHeight="15285" xr2:uid="{4E51E550-2BE2-1645-BA80-54EF4527885D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -345,9 +345,6 @@
     <t>dtype_lst</t>
   </si>
   <si>
-    <t>cciecv_lst</t>
-  </si>
-  <si>
     <t>dtype_pft</t>
   </si>
   <si>
@@ -376,6 +373,9 @@
   </si>
   <si>
     <t>dtype_nh3</t>
+  </si>
+  <si>
+    <t>cciecv_landSurfTemp</t>
   </si>
 </sst>
 </file>
@@ -2175,7 +2175,7 @@
         <v>5</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B85" t="s">
         <v>5</v>
@@ -2197,7 +2197,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B86" t="s">
         <v>5</v>
@@ -2211,13 +2211,13 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>108</v>
+      </c>
+      <c r="B87" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" t="s">
         <v>109</v>
-      </c>
-      <c r="B87" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" t="s">
-        <v>110</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -2225,13 +2225,13 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>110</v>
+      </c>
+      <c r="B88" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" t="s">
         <v>111</v>
-      </c>
-      <c r="B88" t="s">
-        <v>5</v>
-      </c>
-      <c r="C88" t="s">
-        <v>112</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B89" t="s">
         <v>5</v>
@@ -2253,13 +2253,13 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>114</v>
+      </c>
+      <c r="B90" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" t="s">
         <v>115</v>
-      </c>
-      <c r="B90" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" t="s">
-        <v>116</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -2267,13 +2267,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B91" t="s">
         <v>5</v>
       </c>
       <c r="C91" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>

--- a/data/cci/cci-dataType-ecv-mapping.xlsx
+++ b/data/cci/cci-dataType-ecv-mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{988F0833-324E-A94E-ADCC-47810A45B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43199E8C-6F20-480D-A352-BAE349986048}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{988F0833-324E-A94E-ADCC-47810A45B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE081CE9-58DC-4BAF-A278-484111BFF353}"/>
   <bookViews>
-    <workbookView xWindow="39450" yWindow="3285" windowWidth="34515" windowHeight="15285" xr2:uid="{4E51E550-2BE2-1645-BA80-54EF4527885D}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{4E51E550-2BE2-1645-BA80-54EF4527885D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="120">
   <si>
     <t>dtype URI</t>
   </si>
@@ -376,6 +376,12 @@
   </si>
   <si>
     <t>cciecv_landSurfTemp</t>
+  </si>
+  <si>
+    <t>dtype_no2</t>
+  </si>
+  <si>
+    <t>dtype_hcho</t>
   </si>
 </sst>
 </file>
@@ -994,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03066BF4-F4E8-0F4A-A490-1A16D2F31AC9}">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2276,6 +2282,34 @@
         <v>115</v>
       </c>
       <c r="D91" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>118</v>
+      </c>
+      <c r="B92" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" t="s">
+        <v>115</v>
+      </c>
+      <c r="D92" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>119</v>
+      </c>
+      <c r="B93" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" t="s">
+        <v>115</v>
+      </c>
+      <c r="D93" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/cci/cci-dataType-ecv-mapping.xlsx
+++ b/data/cci/cci-dataType-ecv-mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stfc365-my.sharepoint.com/personal/alison_waterfall_stfc_ac_uk/Documents/Documents/GitHub/cci-vocabularies/data/cci/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{988F0833-324E-A94E-ADCC-47810A45B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE081CE9-58DC-4BAF-A278-484111BFF353}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{988F0833-324E-A94E-ADCC-47810A45B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C6C57DC-7461-46B8-B460-A3F4CB49458D}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{4E51E550-2BE2-1645-BA80-54EF4527885D}"/>
+    <workbookView xWindow="38280" yWindow="-60" windowWidth="38640" windowHeight="21120" xr2:uid="{4E51E550-2BE2-1645-BA80-54EF4527885D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="122">
   <si>
     <t>dtype URI</t>
   </si>
@@ -382,6 +382,12 @@
   </si>
   <si>
     <t>dtype_hcho</t>
+  </si>
+  <si>
+    <t>dtype_issp</t>
+  </si>
+  <si>
+    <t>dtype_so2</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03066BF4-F4E8-0F4A-A490-1A16D2F31AC9}">
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2310,6 +2316,34 @@
         <v>115</v>
       </c>
       <c r="D93" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>120</v>
+      </c>
+      <c r="B94" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" t="s">
+        <v>93</v>
+      </c>
+      <c r="D94" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>121</v>
+      </c>
+      <c r="B95" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" t="s">
+        <v>115</v>
+      </c>
+      <c r="D95" t="s">
         <v>7</v>
       </c>
     </row>
